--- a/diseases/d120/1995-1999.xlsx
+++ b/diseases/d120/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5626,9 +5590,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6250,9 +6211,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7019,9 +6977,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7788,9 +7743,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8557,9 +8509,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9326,9 +9275,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10095,9 +10041,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10864,9 +10807,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11633,9 +11573,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12402,9 +12339,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13171,9 +13105,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13940,9 +13871,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14709,9 +14637,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15247,9 +15172,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15871,9 +15793,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16640,9 +16559,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17409,9 +17325,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18178,9 +18091,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18947,9 +18857,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19716,9 +19623,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20485,9 +20389,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21254,9 +21155,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22023,9 +21921,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22792,9 +22687,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23561,9 +23453,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24330,9 +24219,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24868,9 +24754,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25492,9 +25375,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26261,9 +26141,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27030,9 +26907,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27799,9 +27673,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28568,9 +28439,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29337,9 +29205,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30106,9 +29971,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30875,9 +30737,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31644,9 +31503,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32413,9 +32269,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33182,9 +33035,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33949,9 +33799,6 @@
         <v>0</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="S174" t="inlineStr">
